--- a/Assets/Resources/DataFiles/UnknownStageData/1. ExcelFile/UnknownStageLabel.xlsx
+++ b/Assets/Resources/DataFiles/UnknownStageData/1. ExcelFile/UnknownStageLabel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\UnknownStageData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A71082-13F5-4AD9-BB01-A23FD52FA623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DBFAEC-BA24-4EB4-B0A5-396EF7E5673A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8846,7 +8846,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>247</v>
       </c>
@@ -8856,25 +8856,23 @@
       <c r="C2" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D2" s="1">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>204</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>249</v>
       </c>
@@ -8884,21 +8882,19 @@
       <c r="C3" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>205</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
@@ -8912,21 +8908,19 @@
       <c r="C4" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>206</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
@@ -8940,21 +8934,19 @@
       <c r="C5" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
@@ -8968,21 +8960,19 @@
       <c r="C6" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>218</v>
       </c>
+      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
@@ -8996,29 +8986,27 @@
       <c r="C7" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>210</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="G7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="H7" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>258</v>
       </c>
@@ -9028,29 +9016,27 @@
       <c r="C8" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>216</v>
       </c>
+      <c r="H8" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="99" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>260</v>
       </c>
@@ -9060,27 +9046,25 @@
       <c r="C9" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D9" s="1">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>217</v>
       </c>
+      <c r="H9" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="I9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -9092,15 +9076,13 @@
       <c r="C10" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
+      <c r="D10" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
@@ -9114,21 +9096,19 @@
       <c r="C11" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>211</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
@@ -9142,25 +9122,23 @@
       <c r="C12" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="1">
-        <v>2</v>
+      <c r="D12" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>268</v>
       </c>
@@ -9170,29 +9148,27 @@
       <c r="C13" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D13" s="1">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>215</v>
       </c>
+      <c r="H13" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="I13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>270</v>
       </c>
@@ -9202,25 +9178,23 @@
       <c r="C14" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="1">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>213</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>272</v>
       </c>
@@ -9230,21 +9204,19 @@
       <c r="C15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H15" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
@@ -10096,7 +10068,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="53.25" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>247</v>
       </c>
@@ -10106,25 +10078,23 @@
       <c r="C2" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D2" s="1">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>232</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="35.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>249</v>
       </c>
@@ -10134,21 +10104,19 @@
       <c r="C3" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>146</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
@@ -10162,21 +10130,19 @@
       <c r="C4" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="1">
-        <v>2</v>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
@@ -10190,21 +10156,19 @@
       <c r="C5" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>233</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
@@ -10218,21 +10182,19 @@
       <c r="C6" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>234</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
@@ -10246,29 +10208,27 @@
       <c r="C7" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>245</v>
       </c>
+      <c r="H7" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="70.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>258</v>
       </c>
@@ -10278,27 +10238,25 @@
       <c r="C8" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>244</v>
       </c>
+      <c r="H8" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="74.25" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -10310,27 +10268,25 @@
       <c r="C9" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D9" s="1">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>246</v>
       </c>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="90.75" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -10342,15 +10298,13 @@
       <c r="C10" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
+      <c r="D10" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
@@ -10364,21 +10318,19 @@
       <c r="C11" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>240</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
@@ -10392,25 +10344,23 @@
       <c r="C12" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D12" s="1">
-        <v>2</v>
+      <c r="D12" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="54.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>268</v>
       </c>
@@ -10420,29 +10370,27 @@
       <c r="C13" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D13" s="1">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>128</v>
       </c>
+      <c r="G13" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="H13" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="I13" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.3">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>270</v>
       </c>
@@ -10452,25 +10400,23 @@
       <c r="C14" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="D14" s="1">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>238</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="54.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="69" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>272</v>
       </c>
@@ -10480,21 +10426,19 @@
       <c r="C15" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>237</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H15" s="1" t="s">
         <v>145</v>
       </c>
+      <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
@@ -11333,7 +11277,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>247</v>
       </c>
@@ -11358,7 +11302,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="53.25" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>249</v>
       </c>
@@ -11487,7 +11431,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="35.25" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>258</v>
       </c>
@@ -11645,7 +11589,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>270</v>
       </c>

--- a/Assets/Resources/DataFiles/UnknownStageData/1. ExcelFile/UnknownStageLabel.xlsx
+++ b/Assets/Resources/DataFiles/UnknownStageData/1. ExcelFile/UnknownStageLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\UnknownStageData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DBFAEC-BA24-4EB4-B0A5-396EF7E5673A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893E3A2C-2A16-4B06-A73E-E478B5756EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="12" r:id="rId1"/>
@@ -3040,10 +3040,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>s</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Emergency Vent</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7296,6 +7292,10 @@
       </rPr>
       <t>速度提高20%。</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Broken Safe</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="12" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>102</v>
@@ -7978,7 +7978,7 @@
     </row>
     <row r="13" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>116</v>
@@ -8007,7 +8007,7 @@
     </row>
     <row r="14" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>130</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="15" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>135</v>
@@ -9071,7 +9071,7 @@
         <v>261</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>198</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="12" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>200</v>
@@ -9140,10 +9140,10 @@
     </row>
     <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>201</v>
@@ -9170,10 +9170,10 @@
     </row>
     <row r="14" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>202</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="15" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>203</v>
@@ -10236,7 +10236,7 @@
         <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>76</v>
@@ -10336,7 +10336,7 @@
     </row>
     <row r="12" spans="1:10" ht="53.25" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>111</v>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>126</v>
@@ -10383,7 +10383,7 @@
         <v>242</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>129</v>
@@ -10392,7 +10392,7 @@
     </row>
     <row r="14" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>133</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="15" spans="1:10" ht="69" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>142</v>
@@ -11282,22 +11282,22 @@
         <v>247</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -11307,22 +11307,22 @@
         <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -11332,22 +11332,22 @@
         <v>250</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -11357,22 +11357,22 @@
         <v>252</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>291</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -11382,22 +11382,22 @@
         <v>254</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -11407,28 +11407,28 @@
         <v>256</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="35.25" x14ac:dyDescent="0.3">
@@ -11436,28 +11436,28 @@
         <v>258</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -11465,28 +11465,28 @@
         <v>260</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="88.5" x14ac:dyDescent="0.3">
@@ -11494,16 +11494,16 @@
         <v>261</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -11515,126 +11515,126 @@
         <v>263</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="F14" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>

--- a/Assets/Resources/DataFiles/UnknownStageData/1. ExcelFile/UnknownStageLabel.xlsx
+++ b/Assets/Resources/DataFiles/UnknownStageData/1. ExcelFile/UnknownStageLabel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\UnknownStageData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893E3A2C-2A16-4B06-A73E-E478B5756EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4D72FD-E9B6-4718-86C8-B5E0C6CD8DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,33 +97,21 @@
     <t>코어를 뜯어낸다.</t>
   </si>
   <si>
-    <t>정비드론의 코어를 획득합니다.</t>
-  </si>
-  <si>
     <t>Repair it.</t>
   </si>
   <si>
     <t>Rip out the core.</t>
   </si>
   <si>
-    <t>Obtain the Maintenance Drone Core.</t>
-  </si>
-  <si>
     <t>歌う整備ドローン</t>
   </si>
   <si>
     <t>修理する。</t>
   </si>
   <si>
-    <t>持続：防御力が10%増加します。</t>
-  </si>
-  <si>
     <t>コアを取り出す。</t>
   </si>
   <si>
-    <t>整備ドローンのコアを獲得します。</t>
-  </si>
-  <si>
     <t>누르면 안 되는 버튼</t>
   </si>
   <si>
@@ -136,9 +124,6 @@
     <t>Press it.</t>
   </si>
   <si>
-    <t>Move to an Elite Stage.</t>
-  </si>
-  <si>
     <t>Respect the warning.</t>
   </si>
   <si>
@@ -160,9 +145,6 @@
     <t>강제로 연다.</t>
   </si>
   <si>
-    <t>고급 등급의 무작위 장비 2개를 획득합니다.</t>
-  </si>
-  <si>
     <t>Guess the combination.</t>
   </si>
   <si>
@@ -178,9 +160,6 @@
     <t>無理やり開ける。</t>
   </si>
   <si>
-    <t>ランダムな上級等級装備を2個獲得します。</t>
-  </si>
-  <si>
     <t>자기 폭풍</t>
   </si>
   <si>
@@ -190,30 +169,18 @@
     <t>달려서 탈출한다.</t>
   </si>
   <si>
-    <t>인벤토리에서 무작위 아이템 2개를 버립니다.</t>
-  </si>
-  <si>
     <t>바닥에 엎드린다.</t>
   </si>
   <si>
-    <t>모든 골드를 잃습니다.</t>
-  </si>
-  <si>
     <t>Discard some items.</t>
   </si>
   <si>
     <t>Run for the exit.</t>
   </si>
   <si>
-    <t>Discard 2 random items from your inventory.</t>
-  </si>
-  <si>
     <t>Drop to the floor.</t>
   </si>
   <si>
-    <t>Lose all Credits.</t>
-  </si>
-  <si>
     <t>磁気嵐</t>
   </si>
   <si>
@@ -226,18 +193,12 @@
     <t>床に伏せる。</t>
   </si>
   <si>
-    <t>すべてのクレジットを失います。</t>
-  </si>
-  <si>
     <t>소프트웨어 업데이트</t>
   </si>
   <si>
     <t>최신 버전으로 업데이트한다.</t>
   </si>
   <si>
-    <t>안정 버전으로 업데이트한다.</t>
-  </si>
-  <si>
     <t>나중에 다시 알림.</t>
   </si>
   <si>
@@ -271,10 +232,6 @@
     <t>Drink the black tea.</t>
   </si>
   <si>
-    <t>Take damage equal to 60% of maximum HP.
-Persistent: MP recovery increases by 20%.</t>
-  </si>
-  <si>
     <t>ウィリアム自動販売機</t>
   </si>
   <si>
@@ -290,24 +247,15 @@
     <t>금고를 열어본다.</t>
   </si>
   <si>
-    <t>1000크레딧을 획득합니다.</t>
-  </si>
-  <si>
     <t>Open the safe.</t>
   </si>
   <si>
-    <t>Gain 1,000 Credits.</t>
-  </si>
-  <si>
     <t>壊れた金庫</t>
   </si>
   <si>
     <t>金庫を開ける。</t>
   </si>
   <si>
-    <t>1,000クレジットを獲得します。</t>
-  </si>
-  <si>
     <t>길 잃은 배송 로봇</t>
   </si>
   <si>
@@ -338,62 +286,33 @@
     <t>왼쪽으로 간다.</t>
   </si>
   <si>
-    <t>캠프로 이동합니다.</t>
-  </si>
-  <si>
     <t>오른쪽으로 간다.</t>
   </si>
   <si>
-    <t>일반 스테이지로 이동합니다.</t>
-  </si>
-  <si>
     <t>Go left.</t>
   </si>
   <si>
-    <t>Move to Camp.</t>
-  </si>
-  <si>
     <t>Go right.</t>
   </si>
   <si>
-    <t>Move to a Normal Stage.</t>
-  </si>
-  <si>
     <t>非常用ダクト</t>
   </si>
   <si>
     <t>左へ進む。</t>
   </si>
   <si>
-    <t>キャンプへ移動します。</t>
-  </si>
-  <si>
     <t>右へ進む。</t>
   </si>
   <si>
-    <t>通常ステージへ移動します。</t>
-  </si>
-  <si>
     <t>AI 상담실</t>
   </si>
   <si>
     <t>미래에 대한 상담을 한다.</t>
   </si>
   <si>
-    <t>과거에 대한 상담을 한다.</t>
-  </si>
-  <si>
-    <t>최대 체력이 5% 증가합니다.
-지속: 공격력이 5% 감소합니다.</t>
-  </si>
-  <si>
     <t>광고를 건너뛴다.</t>
   </si>
   <si>
-    <t>200크레딧을 지불합니다.
-지속: 이동속도가 5% 증가합니다.</t>
-  </si>
-  <si>
     <t>Ask about the future.</t>
   </si>
   <si>
@@ -403,10 +322,6 @@
     <t>Skip the advertisement.</t>
   </si>
   <si>
-    <t>Pay 200 Credits.
-Persistent: Movement speed increases by 5%.</t>
-  </si>
-  <si>
     <t>AI相談室</t>
   </si>
   <si>
@@ -416,10 +331,6 @@
     <t>過去について相談する。</t>
   </si>
   <si>
-    <t>200クレジットを支払います。
-持続：移動速度が5%増加します。</t>
-  </si>
-  <si>
     <t>고철 압축기</t>
   </si>
   <si>
@@ -444,18 +355,12 @@
     <t>고양이 영상만 본다.</t>
   </si>
   <si>
-    <t>체력을 최대 체력의 20%만큼 회복합니다.</t>
-  </si>
-  <si>
     <t>Install the combat data.</t>
   </si>
   <si>
     <t>Watch only the cat videos.</t>
   </si>
   <si>
-    <t>Restore 20% of maximum HP.</t>
-  </si>
-  <si>
     <t>見知らぬ記憶データ</t>
   </si>
   <si>
@@ -463,56 +368,6 @@
   </si>
   <si>
     <t>猫動画だけを見る。</t>
-  </si>
-  <si>
-    <t>最大HPの20%を回復します。</t>
-  </si>
-  <si>
-    <r>
-      <t>最大HPの30%を回復します。
-次の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>戦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>闘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>のみ：防御力が30%減少します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력을 최대 체력의 30%만큼 회복합니다.
-일회성: 방어력이 30% 감소합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속: 공격력이 5% 증가합니다.
-최대 체력의 30%만큼 피해를 받습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Overcharge</t>
@@ -604,11 +459,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>최대 체력의 60%만큼 피해를 받습니다.
-지속: 이동속도가 20% 증가합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>민트맛 콜라를 마신다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -634,63 +484,6 @@
     <t>거대한 자기 폭풍때문에 건물 전체가 흔들립니다.
 주머니속의 금속 물체들이 요동치기 시작합니다.
 무엇이라도 포기해야 이곳을 벗어날 수 있을겁니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속: 방어력이 10% 증가합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>엘리트 스테이지로 이동합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>50% 확률로 유일 등급의 무작위 장비 1개를 획득합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>인벤토리에서 아이템 3개를 선택하여 버립니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속: 공격력이 8% 증가합니다.
-지속: 방어력이 15% 감소합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력의 60%만큼 피해를 받습니다.
-지속: 공격 속도가 20% 증가합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>방전된 코어를 획득합니다.
-엘리트 스테이지로 이동합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속: 공격력이 5% 증가합니다.
-최대 체력이 5% 감소합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>인벤토리에서 아이템 2개를 선택하여 버립니다.
-400크레딧을 획득합니다.
-고철 큐브 코어를 획득합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속: 스킬 재사용 대기시간이 5% 감소합니다.
-최대 체력의 5%만큼 피해를 받습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력의 60%만큼 피해를 받습니다.
-지속: MP회복력이 20% 증가합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속: 방어력이 10% 증가합니다.
-지속: 공격력이 5% 감소합니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -795,78 +588,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Persistent: Attack increases by 5%.
-Take damage equal to 30% of maximum HP.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Restore 30% of maximum HP.
-Next battle only: Defense decreases by 30%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persistent: Defense increases by 10%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>50% chance to obtain 1 random Unique-grade piece of equipment.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persistent: Attack increases by 8%.
-Persistent: Defense decreases by 15%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Take damage equal to 60% of maximum HP.
-Persistent: Attack speed increases by 20%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Select and discard 3 items from your inventory.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Obtain a Depleted Core.
-Move to an Elite Stage.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persistent: Attack increases by 5%.
-Maximum HP decreases by 5%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Select and discard 2 items from your inventory.
-Gain 400 Credits.
-Obtain the Scrap Cube Core.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persistent: Skill cooldown decreases by 5%.
-Take damage equal to 5% of maximum HP.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maximum HP increases by 5%.
-Persistent: Attack decreases by 5%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persistent: Defense increases by 10%.
-Persistent: Attack decreases by 5%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Take damage equal to 60% of maximum HP.
-Persistent: Movement speed increases by 20%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Obtain 2 random Advanced-grade pieces of equipment.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>工場の</t>
     </r>
@@ -2134,844 +1855,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力が5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。
-最大HPの30%分のダメ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジを受けます。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>エリ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>トステ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジへ移動します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>50%の確率でランダムなユニ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ク等級装備を1個獲得します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>インベントリからアイテムを3個選んで捨てます。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大HPの60%分のダメ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジを受けます。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>速度が20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：スキルのク</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ルダウンが5%減少します。
-最大HPの5%分のダメ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジを受けます。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>インベントリからアイテムを2個選んで捨てます。
-400クレジットを獲得します。
-スクラップキュ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ブコアを獲得します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力が5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。
-最大HPが5%減少します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>放電したコアを獲得します。
-エリ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>トステ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジへ移動します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力が8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：防御力が15%減少します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大HPが5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力が5%減少します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大HPの60%分のダメ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジを受けます。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：移動速度が20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：防御力が10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>撃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力が5%減少します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>インベントリからランダムなアイテムを2個捨てます。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大HPの60%分のダメ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>ジを受けます。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>続</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：MP回復力が20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>増</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>加します。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>stage.unknown.overcharge</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3170,10 +2053,6 @@
     <t>吃下去。</t>
   </si>
   <si>
-    <t>恢复相当于最大生命值30%的生命值。
-仅限下一场战斗：防御力降低30%。</t>
-  </si>
-  <si>
     <t>悄悄关上。</t>
   </si>
   <si>
@@ -3183,24 +2062,15 @@
     <t>修理它。</t>
   </si>
   <si>
-    <t>持续：防御力提高10%。</t>
-  </si>
-  <si>
     <t>拆下核心。</t>
   </si>
   <si>
-    <t>获得维修无人机核心。</t>
-  </si>
-  <si>
     <t>禁止按下的按钮</t>
   </si>
   <si>
     <t>按下。</t>
   </si>
   <si>
-    <t>前往精英关卡。</t>
-  </si>
-  <si>
     <t>尊重警告。</t>
   </si>
   <si>
@@ -3213,30 +2083,18 @@
     <t>强行打开。</t>
   </si>
   <si>
-    <t>随机获得2件高级品质装备。</t>
-  </si>
-  <si>
     <t>磁暴</t>
   </si>
   <si>
     <t>丢弃物品。</t>
   </si>
   <si>
-    <t>从背包中选择并丢弃3件物品。</t>
-  </si>
-  <si>
     <t>跑出去。</t>
   </si>
   <si>
-    <t>从背包中随机丢弃2件物品。</t>
-  </si>
-  <si>
     <t>趴在地上。</t>
   </si>
   <si>
-    <t>失去所有信用点。</t>
-  </si>
-  <si>
     <t>软件更新</t>
   </si>
   <si>
@@ -3246,10 +2104,6 @@
     <t>安装稳定版。</t>
   </si>
   <si>
-    <t>持续：防御力提高10%。
-持续：攻击力降低5%。</t>
-  </si>
-  <si>
     <t>稍后提醒我。</t>
   </si>
   <si>
@@ -3265,19 +2119,12 @@
     <t>喝红茶。</t>
   </si>
   <si>
-    <t>受到相当于最大生命值60%的伤害。
-持续：MP恢复速度提高20%。</t>
-  </si>
-  <si>
     <t>破损的保险柜</t>
   </si>
   <si>
     <t>打开保险柜。</t>
   </si>
   <si>
-    <t>获得1,000信用点。</t>
-  </si>
-  <si>
     <t>迷路的配送机器人</t>
   </si>
   <si>
@@ -3293,46 +2140,27 @@
     <t>向左走。</t>
   </si>
   <si>
-    <t>前往营地。</t>
-  </si>
-  <si>
     <t>向右走。</t>
   </si>
   <si>
-    <t>前往普通关卡。</t>
-  </si>
-  <si>
     <t>AI咨询室</t>
   </si>
   <si>
     <t>咨询未来。</t>
   </si>
   <si>
-    <t>持续：攻击力提高5%。
-最大生命值降低5%。</t>
-  </si>
-  <si>
     <t>咨询过去。</t>
   </si>
   <si>
     <t>跳过广告。</t>
   </si>
   <si>
-    <t>支付200信用点。
-持续：移动速度提高5%。</t>
-  </si>
-  <si>
     <t>废料压缩机</t>
   </si>
   <si>
     <t>放入物品。</t>
   </si>
   <si>
-    <t>从背包中选择并丢弃2件物品。
-获得400信用点。
-获得废料方块核心。</t>
-  </si>
-  <si>
     <t>陌生的记忆数据</t>
   </si>
   <si>
@@ -3340,9 +2168,6 @@
   </si>
   <si>
     <t>只看猫咪视频。</t>
-  </si>
-  <si>
-    <t>恢复相当于最大生命值20%的生命值。</t>
   </si>
   <si>
     <r>
@@ -4014,113 +2839,6 @@
   </si>
   <si>
     <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力提高5%。
-受到相</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>当</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>于最大生命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>30%的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>害。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>走廊正中央有一</t>
     </r>
     <r>
@@ -6650,653 +5368,397 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>有50%的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>概</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>随</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>机</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>获</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>得1件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>独</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>特品</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>质</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>备</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力提高8%。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：防御力降低15%。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>受到相</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>当</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>于最大生命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>60%的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>害。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>速度提高20%。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>获</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>得耗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>尽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>能量的核心。
-前往精英</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>关</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>卡。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：技能冷却</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>时间缩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>短5%。
-受到相</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>当</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>于最大生命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>5%的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>害。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大生命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>提高5%。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：攻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>力降低5%。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>受到相</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>当</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>于最大生命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>60%的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>害。
-持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>：移</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>速度提高20%。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Broken Safe</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 공격력이 &lt;color=#32CD32&gt;8%&lt;/color&gt; 증가합니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 방어력이 &lt;color=#DC3132&gt;15%&lt;/color&gt;: 감소합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 공격력이 &lt;color=#32CD32&gt;5%&lt;/color&gt; 증가합니다.
+최대 체력의 &lt;color=#DC3132&gt;30%&lt;/color&gt;만큼 피해를 받습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 최대 체력의 &lt;color=#32CD32&gt;30%&lt;/color&gt;만큼 회복합니다.
+&lt;color=#8A2BE2&gt;일회성&lt;/color&gt;: 방어력이 &lt;color=#DC3132&gt;30%&lt;/color&gt; 감소합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 방어력이 &lt;color=#32CD32&gt;10%&lt;/color&gt; 증가합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#DAA520&gt;엘리트 스테이지&lt;/color&gt;로 이동합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50% 확률로 유일 등급의 &lt;color=#32CD32&gt;무작위 장비 1개&lt;/color&gt;를 획득합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 등급의 &lt;color=#32CD32&gt;무작위 장비 2개&lt;/color&gt;를 획득합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#DC3132&gt;모든 골드&lt;/color&gt;를 잃습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리에서 &lt;color=#DC3132&gt;무작위 아이템 2개&lt;/color&gt;를 버립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리에서 &lt;color=#DC3132&gt;아이템 3개&lt;/color&gt;를 선택하여 버립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력의 &lt;color=#DC3132&gt;60%&lt;/color&gt;만큼 피해를 받습니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: MP회복력이 &lt;color=#32CD32&gt;20%&lt;/color&gt; 증가합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안정 버전으로 업데이트한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력의 &lt;color=#DC3132&gt;60%&lt;/color&gt;만큼 피해를 받습니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 공격 속도가 &lt;color=#32CD32&gt;20%&lt;/color&gt; 증가합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력의 &lt;color=#DC3132&gt;60%&lt;/color&gt;만큼 피해를 받습니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 이동속도가 &lt;color=#32CD32&gt;20%&lt;/color&gt; 증가합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 방어력이 &lt;color=#32CD32&gt;10%&lt;/color&gt; 증가합니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 공격력이 &lt;color=#DC3132&gt;5%&lt;/color&gt; 감소합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;1000크레딧&lt;/color&gt;을 획득합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;방전된 코어&lt;/color&gt;를 획득합니다.
+&lt;color=#DAA520&gt;엘리트 스테이지&lt;/color&gt;로 이동합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#DAA520&gt;캠프&lt;/color&gt;로 이동합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#DAA520&gt;일반 스테이지&lt;/color&gt;로 이동합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;정비드론의 코어&lt;/color&gt;를 획득합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 공격력이 &lt;color=#32CD32&gt;5%&lt;/color&gt; 증가합니다.
+최대 체력이 &lt;color=#DC3132&gt;5%&lt;/color&gt; 감소합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력이 &lt;color=#32CD32&gt;5%&lt;/color&gt; 증가합니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 공격력이 &lt;color=#DC3132&gt;5%&lt;/color&gt; 감소합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>과거에 대한 상담을 한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리에서 &lt;color=#DC3132&gt;아이템 2개&lt;/color&gt;를 선택하여 버립니다.
+&lt;color=#32CD32&gt;400크레딧&lt;/color&gt;을 획득합니다.
+&lt;color=#32CD32&gt;고철 큐브 코어&lt;/color&gt;를 획득합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 최대 체력의 &lt;color=#32CD32&gt;20%&lt;/color&gt;만큼 회복합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#DC3132&gt;200크레딧&lt;/color&gt;을 지불합니다.
+&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 이동속도가 &lt;color=#32CD32&gt;5%&lt;/color&gt; 증가합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;지속&lt;/color&gt;: 스킬 재사용 대기시간이 5% 감소합니다.
+최대 체력의 &lt;color=#DC3132&gt;5%&lt;/color&gt;만큼 피해를 받습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Attack increases by &lt;color=#32CD32&gt;5%&lt;/color&gt;.
+Take damage equal to &lt;color=#DC3132&gt;30%&lt;/color&gt; of maximum HP.</t>
+  </si>
+  <si>
+    <t>Restore &lt;color=#32CD32&gt;30%&lt;/color&gt; of maximum HP.
+&lt;color=#8A2BE2&gt;Next battle only&lt;/color&gt;: Defense decreases by &lt;color=#DC3132&gt;30%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Defense increases by &lt;color=#32CD32&gt;10%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Move to an &lt;color=#DAA520&gt;Elite Stage&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>50% chance to obtain &lt;color=#32CD32&gt;1 random Unique-grade piece of equipment&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Select and discard &lt;color=#DC3132&gt;3 items&lt;/color&gt; from your inventory.</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Attack increases by &lt;color=#32CD32&gt;8%&lt;/color&gt;.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Defense decreases by &lt;color=#DC3132&gt;15%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Take damage equal to &lt;color=#DC3132&gt;60%&lt;/color&gt; of maximum HP.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Attack speed increases by &lt;color=#32CD32&gt;20%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Gain &lt;color=#32CD32&gt;1,000 Credits&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Obtain a &lt;color=#32CD32&gt;Depleted Core&lt;/color&gt;.
+Move to an &lt;color=#DAA520&gt;Elite Stage&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Move to &lt;color=#DAA520&gt;Camp&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Attack increases by &lt;color=#32CD32&gt;5%&lt;/color&gt;.
+Maximum HP decreases by &lt;color=#DC3132&gt;5%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Select and discard &lt;color=#DC3132&gt;2 items&lt;/color&gt; from your inventory.
+Gain &lt;color=#32CD32&gt;400 Credits&lt;/color&gt;.
+Obtain the &lt;color=#32CD32&gt;Scrap Cube Core&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Skill cooldown decreases by 5%.
+Take damage equal to &lt;color=#DC3132&gt;5%&lt;/color&gt; of maximum HP.</t>
+  </si>
+  <si>
+    <t>Obtain the &lt;color=#32CD32&gt;Maintenance Drone Core&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Obtain &lt;color=#32CD32&gt;2 random Advanced-grade pieces of equipment&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Discard &lt;color=#DC3132&gt;2 random items&lt;/color&gt; from your inventory.</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Defense increases by &lt;color=#32CD32&gt;10%&lt;/color&gt;.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Attack decreases by &lt;color=#DC3132&gt;5%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Take damage equal to &lt;color=#DC3132&gt;60%&lt;/color&gt; of maximum HP.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Movement speed increases by &lt;color=#32CD32&gt;20%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Move to a &lt;color=#DAA520&gt;Normal Stage&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Maximum HP increases by &lt;color=#32CD32&gt;5%&lt;/color&gt;.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Attack decreases by &lt;color=#DC3132&gt;5%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Restore &lt;color=#32CD32&gt;20%&lt;/color&gt; of maximum HP.</t>
+  </si>
+  <si>
+    <t>Lose &lt;color=#DC3132&gt;all Credits&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Take damage equal to &lt;color=#DC3132&gt;60%&lt;/color&gt; of maximum HP.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: MP recovery increases by &lt;color=#32CD32&gt;20%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Pay &lt;color=#DC3132&gt;200 Credits&lt;/color&gt;.
+&lt;color=#8A2BE2&gt;Persistent&lt;/color&gt;: Movement speed increases by &lt;color=#32CD32&gt;5%&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：攻撃力が&lt;color=#32CD32&gt;5%&lt;/color&gt;増加します。
+最大HPの&lt;color=#DC3132&gt;30%&lt;/color&gt;分のダメージを受けます。</t>
+  </si>
+  <si>
+    <t>最大HPの&lt;color=#32CD32&gt;30%&lt;/color&gt;を回復します。
+&lt;color=#8A2BE2&gt;次の戦闘のみ&lt;/color&gt;：防御力が&lt;color=#DC3132&gt;30%&lt;/color&gt;減少します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：防御力が&lt;color=#32CD32&gt;10%&lt;/color&gt;増加します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#DAA520&gt;エリートステージ&lt;/color&gt;へ移動します。</t>
+  </si>
+  <si>
+    <t>50%の確率で&lt;color=#32CD32&gt;ランダムなユニーク等級装備を1個&lt;/color&gt;獲得します。</t>
+  </si>
+  <si>
+    <t>インベントリから&lt;color=#DC3132&gt;アイテムを3個&lt;/color&gt;選んで捨てます。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：攻撃力が&lt;color=#32CD32&gt;8%&lt;/color&gt;増加します。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：防御力が&lt;color=#DC3132&gt;15%&lt;/color&gt;減少します。</t>
+  </si>
+  <si>
+    <t>最大HPの&lt;color=#DC3132&gt;60%&lt;/color&gt;分のダメージを受けます。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：攻撃速度が&lt;color=#32CD32&gt;20%&lt;/color&gt;増加します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;1,000クレジット&lt;/color&gt;を獲得します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;放電したコア&lt;/color&gt;を獲得します。
+&lt;color=#DAA520&gt;エリートステージ&lt;/color&gt;へ移動します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#DAA520&gt;キャンプ&lt;/color&gt;へ移動します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：攻撃力が&lt;color=#32CD32&gt;5%&lt;/color&gt;増加します。
+最大HPが&lt;color=#DC3132&gt;5%&lt;/color&gt;減少します。</t>
+  </si>
+  <si>
+    <t>インベントリから&lt;color=#DC3132&gt;アイテムを2個&lt;/color&gt;選んで捨てます。
+&lt;color=#32CD32&gt;400クレジット&lt;/color&gt;を獲得します。
+&lt;color=#32CD32&gt;スクラップキューブコア&lt;/color&gt;を獲得します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：スキルのクールダウンが5%減少します。
+最大HPの&lt;color=#DC3132&gt;5%&lt;/color&gt;分のダメージを受けます。</t>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;整備ドローンのコア&lt;/color&gt;を獲得します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#32CD32&gt;ランダムな上級等級装備を2個&lt;/color&gt;獲得します。</t>
+  </si>
+  <si>
+    <t>インベントリから&lt;color=#DC3132&gt;ランダムなアイテムを2個&lt;/color&gt;捨てます。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：防御力が&lt;color=#32CD32&gt;10%&lt;/color&gt;増加します。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：攻撃力が&lt;color=#DC3132&gt;5%&lt;/color&gt;減少します。</t>
+  </si>
+  <si>
+    <t>最大HPの&lt;color=#DC3132&gt;60%&lt;/color&gt;分のダメージを受けます。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：移動速度が&lt;color=#32CD32&gt;20%&lt;/color&gt;増加します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#DAA520&gt;通常ステージ&lt;/color&gt;へ移動します。</t>
+  </si>
+  <si>
+    <t>最大HPが&lt;color=#32CD32&gt;5%&lt;/color&gt;増加します。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：攻撃力が&lt;color=#DC3132&gt;5%&lt;/color&gt;減少します。</t>
+  </si>
+  <si>
+    <t>最大HPの&lt;color=#32CD32&gt;20%&lt;/color&gt;を回復します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#DC3132&gt;すべてのクレジット&lt;/color&gt;を失います。</t>
+  </si>
+  <si>
+    <t>最大HPの&lt;color=#DC3132&gt;60%&lt;/color&gt;分のダメージを受けます。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：MP回復力が&lt;color=#32CD32&gt;20%&lt;/color&gt;増加します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#DC3132&gt;200クレジット&lt;/color&gt;を支払います。
+&lt;color=#8A2BE2&gt;持続&lt;/color&gt;：移動速度が&lt;color=#32CD32&gt;5%&lt;/color&gt;増加します。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：攻击力提高&lt;color=#32CD32&gt;5%&lt;/color&gt;。
+受到相当于最大生命值&lt;color=#DC3132&gt;30%&lt;/color&gt;的伤害。</t>
+  </si>
+  <si>
+    <t>恢复相当于最大生命值&lt;color=#32CD32&gt;30%&lt;/color&gt;的生命值。
+&lt;color=#8A2BE2&gt;仅限下一场战斗&lt;/color&gt;：防御力降低&lt;color=#DC3132&gt;30%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：防御力提高&lt;color=#32CD32&gt;10%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>前往&lt;color=#DAA520&gt;精英关卡&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>有50%的概率随机获得&lt;color=#32CD32&gt;1件独特品质装备&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>从背包中选择并丢弃&lt;color=#DC3132&gt;3件物品&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：攻击力提高&lt;color=#32CD32&gt;8%&lt;/color&gt;。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：防御力降低&lt;color=#DC3132&gt;15%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>受到相当于最大生命值&lt;color=#DC3132&gt;60%&lt;/color&gt;的伤害。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：攻击速度提高&lt;color=#32CD32&gt;20%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>获得&lt;color=#32CD32&gt;1,000信用点&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>获得&lt;color=#32CD32&gt;耗尽能量的核心&lt;/color&gt;。
+前往&lt;color=#DAA520&gt;精英关卡&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>前往&lt;color=#DAA520&gt;营地&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：攻击力提高&lt;color=#32CD32&gt;5%&lt;/color&gt;。
+最大生命值降低&lt;color=#DC3132&gt;5%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>从背包中选择并丢弃&lt;color=#DC3132&gt;2件物品&lt;/color&gt;。
+获得&lt;color=#32CD32&gt;400信用点&lt;/color&gt;。
+获得&lt;color=#32CD32&gt;废料方块核心&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：技能冷却时间缩短5%。
+受到相当于最大生命值&lt;color=#DC3132&gt;5%&lt;/color&gt;的伤害。</t>
+  </si>
+  <si>
+    <t>获得&lt;color=#32CD32&gt;维修无人机核心&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>随机获得&lt;color=#32CD32&gt;2件高级品质装备&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>从背包中随机丢弃&lt;color=#DC3132&gt;2件物品&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：防御力提高&lt;color=#32CD32&gt;10%&lt;/color&gt;。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：攻击力降低&lt;color=#DC3132&gt;5%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>受到相当于最大生命值&lt;color=#DC3132&gt;60%&lt;/color&gt;的伤害。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：移动速度提高&lt;color=#32CD32&gt;20%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>前往&lt;color=#DAA520&gt;普通关卡&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>最大生命值提高&lt;color=#32CD32&gt;5%&lt;/color&gt;。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：攻击力降低&lt;color=#DC3132&gt;5%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>恢复相当于最大生命值&lt;color=#32CD32&gt;20%&lt;/color&gt;的生命值。</t>
+  </si>
+  <si>
+    <t>失去&lt;color=#DC3132&gt;所有信用点&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>受到相当于最大生命值&lt;color=#DC3132&gt;60%&lt;/color&gt;的伤害。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：MP恢复速度提高&lt;color=#32CD32&gt;20%&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>支付&lt;color=#DC3132&gt;200信用点&lt;/color&gt;。
+&lt;color=#8A2BE2&gt;持续&lt;/color&gt;：移动速度提高&lt;color=#32CD32&gt;5%&lt;/color&gt;。</t>
   </si>
 </sst>
 </file>
@@ -7386,29 +5848,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7641,20 +6099,87 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{B1A84C19-50D8-475D-B6E6-B81E350A805C}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="ko-KR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200005502" version="1.0.0.13" store="wa200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;Xcy7fAeXSL6Ms6w-iA_Bf&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{877946DF-CA4C-4F98-91F4-72C2B372F7CD}">
+  <we:reference id="wa200010215" version="2.0.0.0" store="ko-KR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010215" version="2.0.0.0" store="WA200010215" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="bps.codex_control.document_id" value="&quot;062ec6b1-dfba-42cc-94d2-20dc98dab0b4&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="101.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="85.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="85.125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="86.25" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.375" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="15.375" style="1" customWidth="1"/>
@@ -7668,48 +6193,48 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>247</v>
+      <c r="A2" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>170</v>
+      <c r="C2" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>148</v>
+      <c r="E2" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -7717,24 +6242,22 @@
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>249</v>
+      <c r="A3" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>171</v>
+      <c r="C3" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>147</v>
+      <c r="E3" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>15</v>
@@ -7742,284 +6265,270 @@
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>250</v>
+      <c r="A4" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>173</v>
+      <c r="E4" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>252</v>
+      <c r="A5" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>152</v>
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>174</v>
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>254</v>
+      <c r="A6" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>153</v>
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>175</v>
+        <v>38</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>256</v>
+      <c r="A7" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>172</v>
+        <v>45</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>176</v>
+        <v>46</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>258</v>
+      <c r="A8" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>154</v>
+        <v>56</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="66" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>183</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>261</v>
+      <c r="A10" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>161</v>
+        <v>126</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>263</v>
+      <c r="A11" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>162</v>
+        <v>77</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>179</v>
+        <v>78</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>265</v>
+      <c r="A12" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>104</v>
+        <v>86</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>267</v>
+      <c r="A13" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>157</v>
+        <v>93</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>269</v>
+      <c r="A14" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>158</v>
+        <v>102</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>181</v>
+        <v>103</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>4</v>
@@ -8027,763 +6536,32 @@
       <c r="G14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>271</v>
+      <c r="A15" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>159</v>
+        <v>107</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>182</v>
+        <v>108</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-    </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-    </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-    </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-    </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B65" s="2"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-    </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-    </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-    </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-    </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-    </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-    </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-    </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-    </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-    </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -8800,11 +6578,11 @@
     <col min="2" max="2" width="32.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="97.875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="43.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="14.375" style="1" customWidth="1"/>
@@ -8817,50 +6595,50 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>190</v>
+    <row r="2" spans="1:9" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>204</v>
+      <c r="E2" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
@@ -8868,25 +6646,22 @@
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>249</v>
+    <row r="3" spans="1:9" ht="132" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>192</v>
+      <c r="C3" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>205</v>
+      <c r="E3" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>18</v>
@@ -8894,295 +6669,270 @@
       <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>191</v>
+    <row r="4" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+        <v>298</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>193</v>
+    <row r="5" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>287</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>194</v>
+    <row r="6" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>207</v>
+        <v>40</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>299</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="165" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="165" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>292</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="99" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F9" s="1" t="s">
+    <row r="11" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>200</v>
+    <row r="12" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+        <v>303</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>201</v>
+    <row r="13" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>212</v>
+        <v>96</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>308</v>
+      </c>
     </row>
-    <row r="14" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>202</v>
+    <row r="14" spans="1:9" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>213</v>
+        <v>104</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>7</v>
@@ -9190,823 +6940,106 @@
       <c r="G14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>203</v>
+    <row r="15" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>214</v>
+        <v>110</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+        <v>305</v>
+      </c>
     </row>
     <row r="17" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="19" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="20" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="22" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="23" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="25" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="28" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="31" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
     </row>
     <row r="35" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
     </row>
-    <row r="37" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
+    <row r="49" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="51" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="53" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="62" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="63" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="64" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="2"/>
     </row>
-    <row r="38" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="40" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="43" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-    </row>
-    <row r="58" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-    </row>
-    <row r="59" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-    </row>
-    <row r="60" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-    </row>
-    <row r="62" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-    </row>
-    <row r="64" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B65" s="2"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-      <c r="J115" s="2"/>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-      <c r="J119" s="2"/>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-      <c r="J120" s="2"/>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-    </row>
+    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="90" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="91" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="92" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="93" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="94" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="95" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="96" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="97" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="98" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="99" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="101" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="102" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="103" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="104" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="105" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="106" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="107" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="108" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="109" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="110" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="111" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="113" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="114" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="115" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="116" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="117" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="118" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="119" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="120" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="121" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10022,11 +7055,11 @@
     <col min="2" max="2" width="25.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="92.125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="38.5" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="14.375" style="1" customWidth="1"/>
@@ -10041,48 +7074,48 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="53.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>247</v>
+    <row r="2" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>219</v>
+      <c r="C2" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>232</v>
+      <c r="E2" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
@@ -10090,25 +7123,22 @@
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>249</v>
+    <row r="3" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>220</v>
+      <c r="C3" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>146</v>
+      <c r="E3" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>21</v>
@@ -10116,295 +7146,271 @@
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>250</v>
+    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+        <v>323</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="34.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>252</v>
+      <c r="A5" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>222</v>
+        <v>34</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>233</v>
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="53.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>254</v>
+      <c r="A6" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>223</v>
+        <v>42</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>234</v>
+        <v>43</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>313</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+        <v>324</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>256</v>
+    <row r="7" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" s="2"/>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="70.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="74.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>260</v>
+    <row r="9" spans="1:10" ht="165" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>225</v>
+        <v>69</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>236</v>
+        <v>70</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J9" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="90.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>261</v>
+      <c r="A10" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>226</v>
+        <v>75</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+        <v>317</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="53.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>263</v>
+    <row r="11" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>227</v>
+        <v>82</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>240</v>
+        <v>83</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>265</v>
+      <c r="A12" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>229</v>
+        <v>90</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>113</v>
+        <v>319</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+        <v>328</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>267</v>
+    <row r="13" spans="1:10" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>228</v>
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>239</v>
+        <v>100</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>333</v>
+      </c>
     </row>
-    <row r="14" spans="1:10" ht="84" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>269</v>
+    <row r="14" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>230</v>
+        <v>105</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>238</v>
+        <v>106</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>11</v>
@@ -10412,819 +7418,106 @@
       <c r="G14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="69" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>271</v>
+    <row r="15" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>231</v>
+        <v>112</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>237</v>
+        <v>113</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+        <v>330</v>
+      </c>
     </row>
     <row r="17" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="20" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="23" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="26" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="29" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="32" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
     </row>
     <row r="35" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
     </row>
-    <row r="36" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
+    <row r="49" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="51" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="53" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="54" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="62" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="63" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="64" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="2"/>
     </row>
-    <row r="38" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="41" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="44" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-    </row>
-    <row r="58" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-    </row>
-    <row r="59" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-    </row>
-    <row r="60" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-    </row>
-    <row r="62" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-    </row>
-    <row r="64" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B65" s="2"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-      <c r="J115" s="2"/>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-      <c r="J119" s="2"/>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-      <c r="J120" s="2"/>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-    </row>
+    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="90" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="91" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="92" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="93" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="94" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="95" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="96" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="97" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="98" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="99" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="101" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="102" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="103" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="104" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="105" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="106" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="107" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="108" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="109" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="110" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="111" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="113" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="114" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="115" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="116" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="117" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="118" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="119" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="120" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="121" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11250,394 +7543,372 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+    <row r="2" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="53.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+    <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="36.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>301</v>
+      <c r="A7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>356</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="35.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="3" t="s">
+    <row r="8" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="99" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="69" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="88.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>353</v>
+      </c>
     </row>
-    <row r="13" spans="1:9" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>328</v>
+    <row r="13" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C14" s="8" t="s">
+    <row r="14" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
